--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-12-2025.xlsx
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£35.65</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£87.37</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-thermal-laminate-insulation-board?variant=55597627507072 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
